--- a/reports/devops-juniors-israel-2026-W42.xlsx
+++ b/reports/devops-juniors-israel-2026-W42.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="290" uniqueCount="290">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="299" uniqueCount="299">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-12T15:13:30</t>
+    <t xml:space="preserve">2026-10-13T14:04:55</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -151,6 +151,24 @@
     <t xml:space="preserve">First Seen</t>
   </si>
   <si>
+    <t xml:space="preserve">Developer Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jfrog</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv/ Netanya, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Active Directory, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://join.jfrog.com/job/?job=8264438&amp;gh_jid=8264438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-13</t>
+  </si>
+  <si>
     <t xml:space="preserve">Development Operations Engineer</t>
   </si>
   <si>
@@ -169,580 +187,592 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rapyd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calanit by one</t>
+  </si>
+  <si>
+    <t xml:space="preserve">North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Final</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cross River</t>
+  </si>
+  <si>
+    <t xml:space="preserve">West Jerusalem, Jerusalem District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Networking, Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Upwind Security</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Technical Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-18</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Torq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Network Operations Center</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Compie Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Docker, Kubernetes, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-center-at-compie-technologies-4478769750</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SPD Hosting LTD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, Networking, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-spd-hosting-ltd-4476095499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netanya, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nebius</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Analyst</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Confidential Careers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4474046133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Raanana</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Operations Engineer II</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWeber</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Uluberia-II,</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Via</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Berlin, Germany</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Amazon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">yes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
+  </si>
+  <si>
     <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
   </si>
   <si>
     <t xml:space="preserve">F5</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
   </si>
   <si>
     <t xml:space="preserve">2026-09-09</t>
   </si>
   <si>
-    <t xml:space="preserve">Student DevOps Engineer- CxP Commercial Foundation Services</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SAP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raanana, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Terraform/IaC, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-devops-engineer-cxp-commercial-foundation-services-at-sap-4436819328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-20</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rapyd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-team-leader-at-rapyd-4428470164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calanit by one</t>
-  </si>
-  <si>
-    <t xml:space="preserve">North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Terraform/IaC, Networking, Monitoring, Virtualization, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-calanit-by-one-4478305717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System &amp; Infrastructure Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Final</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat HaSharon, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-infrastructure-engineer-at-final-4475581791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-30</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Upwind Security</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ramat Gan, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-monitoring-engineer-student-position-at-upwind-security-4476759903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-08</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Technical Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">iGATES - INFORMATION GATES Ltd</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, CI/CD, Git, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-technical-operations-engineer-at-igates-information-gates-ltd-4452212223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-18</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Security Analyst (Student Position)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineer Student, SPIV team</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Amazon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa, Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, CI/CD, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Production Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Torq</t>
-  </si>
-  <si>
-    <t xml:space="preserve">israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/torq/jobs/6179167004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-04</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cye</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-09</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Operations Student - Nights &amp; Weekend shifts</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Voyantis</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Git, Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-operations-student-nights-weekend-shifts-at-voyantis-4473649691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">System Administrator</t>
+    <t xml:space="preserve">Tata Consultancy Services</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4477961931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Engineer- Student Position</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Global-e</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
   </si>
   <si>
     <t xml:space="preserve">Sela</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Docker, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-sela-4476025268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Shavit Software</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rosh HaAyin, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Monitoring, Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-shavit-software-4478393138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Software Engineering INTERN</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Microsoft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Raft Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Hozek Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Fetcherr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Netanya, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-14</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Network Operations &amp; Control</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/network-operations-control-at-shavit-software-4476158339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-06</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nebius</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Cloud (any), Networking, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Analyst</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Confidential Careers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-analyst-at-confidential-careers-4474046133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud Platform Engineer - Student (Java)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/cloud-platform-engineer-student-java-at-sap-4457493270</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Engineer- Student Position</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Global-e</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4475685553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Employer Branding Student (Temporary )</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Nice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Raanana</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://boards.eu.greenhouse.io/nice/jobs/4912601101?gh_jid=4912601101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-01</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Operations Engineer II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWeber</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Uluberia-II,</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-operations-engineer-ii-aweber-1136778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-10</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Working Student, Legal (German-speaking)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Via</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Berlin, Germany</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/via/jobs/8585955002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-07-29</t>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-system-administrator-at-sela-4476440697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">System Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paragon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-engineer-at-paragon-4425617619</t>
   </si>
   <si>
     <t xml:space="preserve">Student Success Coach</t>
@@ -769,6 +799,9 @@
     <t xml:space="preserve">What to learn / where to start</t>
   </si>
   <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
     <t xml:space="preserve">Troubleshooting</t>
   </si>
   <si>
@@ -781,27 +814,24 @@
     <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
   </si>
   <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
     <t xml:space="preserve">Bash/Shell</t>
   </si>
   <si>
     <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
     <t xml:space="preserve">Networking</t>
   </si>
   <si>
@@ -820,36 +850,36 @@
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
     <t xml:space="preserve">AWS</t>
   </si>
   <si>
     <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
   </si>
   <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
     <t xml:space="preserve">CI/CD</t>
   </si>
   <si>
     <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
   </si>
   <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
     <t xml:space="preserve">GCP</t>
   </si>
   <si>
     <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
   </si>
   <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
     <t xml:space="preserve">Count</t>
   </si>
   <si>
@@ -881,9 +911,6 @@
   </si>
   <si>
     <t xml:space="preserve">Error</t>
-  </si>
-  <si>
-    <t xml:space="preserve">yes</t>
   </si>
 </sst>
 </file>
@@ -1008,7 +1035,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
@@ -1016,7 +1043,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8">
@@ -1024,7 +1051,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="9">
@@ -1114,7 +1141,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1122,7 +1149,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1130,7 +1157,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1172,7 +1199,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>33</v>
+        <v>35</v>
       </c>
     </row>
     <row r="30">
@@ -1180,7 +1207,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="31">
@@ -1199,9 +1226,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="60" customWidth="1"/>
-    <col min="3" max="3" width="32" customWidth="1"/>
-    <col min="4" max="4" width="43" customWidth="1"/>
+    <col min="2" max="2" width="59" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
+    <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
     <col min="7" max="7" width="60" customWidth="1"/>
@@ -1256,7 +1283,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1265,7 +1292,7 @@
         <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>49</v>
@@ -1288,7 +1315,7 @@
         <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="F3" s="3">
         <v>100</v>
@@ -1320,7 +1347,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1349,25 +1376,25 @@
         <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6">
@@ -1375,31 +1402,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7">
@@ -1407,31 +1434,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
     </row>
     <row r="8">
@@ -1439,13 +1466,13 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
@@ -1454,16 +1481,16 @@
         <v>84</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9">
@@ -1471,13 +1498,13 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>26</v>
@@ -1486,16 +1513,16 @@
         <v>83</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="10">
@@ -1503,13 +1530,13 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
@@ -1518,16 +1545,16 @@
         <v>80</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="11">
@@ -1535,13 +1562,13 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>26</v>
@@ -1550,16 +1577,16 @@
         <v>74</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="12">
@@ -1567,13 +1594,13 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>26</v>
@@ -1582,16 +1609,16 @@
         <v>70</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="13">
@@ -1599,13 +1626,13 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
@@ -1614,16 +1641,16 @@
         <v>68</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1631,13 +1658,13 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>27</v>
@@ -1646,16 +1673,16 @@
         <v>61</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
     </row>
     <row r="15">
@@ -1663,13 +1690,13 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="E15" s="3" t="s">
         <v>28</v>
@@ -1678,16 +1705,16 @@
         <v>57</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
@@ -1695,13 +1722,13 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="E16" s="3" t="s">
         <v>27</v>
@@ -1710,16 +1737,16 @@
         <v>54</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
     </row>
     <row r="17">
@@ -1727,31 +1754,31 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -1759,31 +1786,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
     </row>
     <row r="19">
@@ -1791,31 +1818,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
     </row>
     <row r="20">
@@ -1823,31 +1850,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F20" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
@@ -1855,31 +1882,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F21" s="3">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
     </row>
     <row r="22">
@@ -1887,31 +1914,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
     </row>
     <row r="23">
@@ -1919,31 +1946,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="3">
         <v>27</v>
       </c>
-      <c r="F23" s="3">
-        <v>34</v>
-      </c>
       <c r="G23" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>159</v>
+        <v>74</v>
       </c>
     </row>
     <row r="24">
@@ -1951,31 +1978,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
     </row>
     <row r="25">
@@ -1983,31 +2010,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26">
@@ -2015,31 +2042,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2077,9 +2104,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="60" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="43" customWidth="1"/>
+    <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -2092,7 +2119,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>173</v>
+        <v>178</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2107,22 +2134,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
     </row>
     <row r="2">
@@ -2136,7 +2163,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2145,10 +2172,10 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
         <v>49</v>
@@ -2157,7 +2184,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
@@ -2171,7 +2198,7 @@
         <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="E3" s="3">
         <v>100</v>
@@ -2180,7 +2207,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2192,7 +2219,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>33</v>
+        <v>27</v>
       </c>
     </row>
     <row r="4">
@@ -2206,7 +2233,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2215,7 +2242,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2227,7 +2254,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>53</v>
+        <v>54</v>
       </c>
     </row>
     <row r="5">
@@ -2238,112 +2265,112 @@
         <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>53</v>
+        <v>65</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E5" s="3">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="K5" s="3">
-        <v>53</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E6" s="3">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="K6" s="3">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>78</v>
+        <v>50</v>
       </c>
       <c r="K7" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
@@ -2352,33 +2379,33 @@
         <v>84</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I8" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K8" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>26</v>
@@ -2387,33 +2414,33 @@
         <v>83</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K9" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
@@ -2422,33 +2449,33 @@
         <v>80</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="K10" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>26</v>
@@ -2457,33 +2484,33 @@
         <v>74</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="K11" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>26</v>
@@ -2492,33 +2519,33 @@
         <v>70</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="K12" s="3">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
@@ -2527,33 +2554,33 @@
         <v>68</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>33</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>27</v>
@@ -2562,33 +2589,33 @@
         <v>61</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="K14" s="3">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>28</v>
@@ -2597,33 +2624,33 @@
         <v>57</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I15" s="3" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="J15" s="3" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="K15" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>27</v>
@@ -2632,159 +2659,159 @@
         <v>54</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H16" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="J16" s="3" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="K16" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H17" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>131</v>
+        <v>50</v>
       </c>
       <c r="K17" s="3">
-        <v>47</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>78</v>
+        <v>138</v>
       </c>
       <c r="K18" s="3">
-        <v>7</v>
+        <v>48</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="K19" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>67</v>
+        <v>144</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E20" s="3">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="K20" s="3">
         <v>0</v>
@@ -2792,223 +2819,223 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E21" s="3">
-        <v>39</v>
+        <v>34</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>62</v>
+        <v>105</v>
       </c>
       <c r="K21" s="3">
-        <v>53</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="K22" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="3">
         <v>27</v>
       </c>
-      <c r="E23" s="3">
-        <v>34</v>
-      </c>
       <c r="F23" s="3" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>159</v>
+        <v>74</v>
       </c>
       <c r="K23" s="3">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>150</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>53</v>
+        <v>164</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>62</v>
+        <v>167</v>
       </c>
       <c r="K24" s="3">
-        <v>53</v>
+        <v>60</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>165</v>
+        <v>124</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>78</v>
+        <v>172</v>
       </c>
       <c r="K25" s="3">
-        <v>7</v>
+        <v>41</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>120</v>
+        <v>173</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>169</v>
+        <v>135</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H26" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>171</v>
+        <v>176</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>172</v>
+        <v>177</v>
       </c>
       <c r="K26" s="3">
-        <v>59</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>179</v>
+        <v>154</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>25</v>
@@ -3017,512 +3044,603 @@
         <v>24</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="K27" s="3">
-        <v>40</v>
+        <v>55</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>128</v>
+        <v>59</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>140</v>
+        <v>192</v>
       </c>
       <c r="K28" s="3">
-        <v>0</v>
+        <v>32</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>188</v>
+        <v>193</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>141</v>
+        <v>194</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>181</v>
+        <v>196</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>190</v>
+        <v>197</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>191</v>
+        <v>198</v>
       </c>
       <c r="K29" s="3">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>150</v>
+        <v>199</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>128</v>
+        <v>141</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>195</v>
+        <v>167</v>
       </c>
       <c r="K30" s="3">
-        <v>54</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>196</v>
+        <v>203</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>197</v>
+        <v>204</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>53</v>
+        <v>135</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>198</v>
+        <v>205</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>199</v>
+        <v>206</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>200</v>
+        <v>207</v>
       </c>
       <c r="K31" s="3">
-        <v>31</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>201</v>
+        <v>208</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>202</v>
+        <v>209</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>203</v>
+        <v>141</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E32" s="3">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>206</v>
+        <v>167</v>
       </c>
       <c r="K32" s="3">
-        <v>13</v>
+        <v>60</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>101</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>147</v>
+        <v>102</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E33" s="3">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H33" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>172</v>
+        <v>138</v>
       </c>
       <c r="K33" s="3">
-        <v>59</v>
+        <v>48</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
+        <v>4</v>
+      </c>
+      <c r="F34" s="3" t="s">
+        <v>218</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="J34" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="K34" s="3">
         <v>12</v>
-      </c>
-      <c r="F34" s="3" t="s">
-        <v>213</v>
-      </c>
-      <c r="G34" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
-        <v>214</v>
-      </c>
-      <c r="J34" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="K34" s="3">
-        <v>6</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>147</v>
+        <v>223</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E35" s="3">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>217</v>
+        <v>224</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>218</v>
+        <v>225</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>172</v>
+        <v>226</v>
       </c>
       <c r="K35" s="3">
-        <v>59</v>
+        <v>33</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>58</v>
+        <v>228</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>59</v>
+        <v>229</v>
       </c>
       <c r="D36" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>8</v>
-      </c>
-      <c r="F36" s="3" t="s">
-        <v>220</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F36" s="3"/>
       <c r="G36" s="3" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>131</v>
+        <v>231</v>
       </c>
       <c r="K36" s="3">
-        <v>47</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>222</v>
+        <v>232</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>223</v>
+        <v>233</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>165</v>
+        <v>234</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E37" s="3">
-        <v>8</v>
-      </c>
-      <c r="F37" s="3" t="s">
-        <v>224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F37" s="3"/>
       <c r="G37" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>225</v>
+        <v>236</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>140</v>
+        <v>62</v>
       </c>
       <c r="K37" s="3">
-        <v>0</v>
+        <v>54</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>226</v>
+        <v>237</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>227</v>
+        <v>238</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>228</v>
+        <v>59</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E38" s="3">
-        <v>4</v>
-      </c>
-      <c r="F38" s="3" t="s">
-        <v>229</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="F38" s="3"/>
       <c r="G38" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="K38" s="3">
-        <v>11</v>
+        <v>34</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>232</v>
+        <v>154</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>234</v>
+        <v>160</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E39" s="3">
-        <v>4</v>
-      </c>
-      <c r="F39" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="F39" s="3"/>
+      <c r="G39" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="G39" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="H39" s="3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>237</v>
+        <v>50</v>
       </c>
       <c r="K39" s="3">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>238</v>
+        <v>154</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>240</v>
+        <v>59</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
         <v>0</v>
       </c>
       <c r="F40" s="3"/>
       <c r="G40" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>242</v>
+        <v>177</v>
       </c>
       <c r="K40" s="3">
-        <v>75</v>
+        <v>1</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>245</v>
+        <v>160</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E41" s="3">
         <v>0</v>
       </c>
       <c r="F41" s="3"/>
       <c r="G41" s="3" t="s">
-        <v>178</v>
+        <v>235</v>
       </c>
       <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3"/>
+      <c r="G42" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>0</v>
+      </c>
+      <c r="F43" s="3"/>
+      <c r="G43" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="K43" s="3">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="H44" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="I41" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="J41" s="3" t="s">
-        <v>247</v>
-      </c>
-      <c r="K41" s="3">
-        <v>68</v>
+      <c r="I44" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="K44" s="3">
+        <v>69</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K41"/>
+  <autoFilter ref="A1:K44"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3564,6 +3682,9 @@
     <hyperlink ref="I39" r:id="rId38"/>
     <hyperlink ref="I40" r:id="rId39"/>
     <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3572,8 +3693,8 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="32" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="24" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3594,10 +3715,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3605,127 +3726,169 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>136</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>137</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D2" s="3">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>138</v>
+        <v>48</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>139</v>
+        <v>49</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>141</v>
+        <v>76</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>40</v>
+        <v>84</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>143</v>
+        <v>78</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>144</v>
+        <v>79</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>150</v>
+        <v>128</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>151</v>
+        <v>129</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>36</v>
+        <v>48</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>152</v>
+        <v>131</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>184</v>
+        <v>144</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>185</v>
+        <v>145</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D5" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>186</v>
+        <v>147</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>187</v>
+        <v>148</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>222</v>
+        <v>154</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="C6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D6" s="3">
-        <v>8</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>224</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="E6" s="3"/>
       <c r="F6" s="3" t="s">
-        <v>225</v>
+        <v>242</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>140</v>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D7" s="3">
+        <v>0</v>
+      </c>
+      <c r="E7" s="3"/>
+      <c r="F7" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G7" s="3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D8" s="3">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3"/>
+      <c r="F8" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>50</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G6"/>
+  <autoFilter ref="A1:G8"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
     <hyperlink ref="F5" r:id="rId4"/>
     <hyperlink ref="F6" r:id="rId5"/>
+    <hyperlink ref="F7" r:id="rId6"/>
+    <hyperlink ref="F8" r:id="rId7"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3740,178 +3903,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>251</v>
+        <v>218</v>
       </c>
       <c r="B2" s="3">
-        <v>25</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="B3" s="3">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>229</v>
+        <v>264</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="B6" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="B7" s="3">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="B8" s="3">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
       <c r="B9" s="3">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="B10" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
       <c r="B12" s="3">
         <v>8</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="B14" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="B16" s="3">
         <v>5</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
     </row>
   </sheetData>
@@ -3931,10 +4094,10 @@
         <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2">
@@ -3942,10 +4105,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="3">
@@ -3953,10 +4116,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4">
@@ -3964,10 +4127,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5">
@@ -3978,7 +4141,7 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
     </row>
     <row r="6">
@@ -3989,7 +4152,7 @@
         <v>1</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7">
@@ -4000,7 +4163,7 @@
         <v>1</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
     </row>
   </sheetData>
@@ -4021,13 +4184,13 @@
         <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2">
@@ -4035,10 +4198,10 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="D2" s="3"/>
     </row>
@@ -4047,10 +4210,10 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="D3" s="3"/>
     </row>
@@ -4062,7 +4225,7 @@
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>289</v>
+        <v>235</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W42.xlsx
+++ b/reports/devops-juniors-israel-2026-W42.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="279">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="313" uniqueCount="313">
   <si>
     <t xml:space="preserve">Metric</t>
   </si>
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-14T11:42:37</t>
+    <t xml:space="preserve">2026-10-15T11:19:53</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,15 +94,21 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
+  </si>
+  <si>
     <t xml:space="preserve">Help Desk / IT Support</t>
   </si>
   <si>
-    <t xml:space="preserve">Trainee / Bootcamp Grad</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior SysAdmin / Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -181,15 +187,30 @@
     <t xml:space="preserve">2026-09-16</t>
   </si>
   <si>
+    <t xml:space="preserve">DevOps &amp; Cloud Infrastructure Intern</t>
+  </si>
+  <si>
+    <t xml:space="preserve">F5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Docker, Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/devops-cloud-infrastructure-intern-at-f5-4464650168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-09</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Team Leader</t>
   </si>
   <si>
     <t xml:space="preserve">Rapyd</t>
   </si>
   <si>
-    <t xml:space="preserve">Tel Aviv-Yafo, Tel Aviv District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Python, Bash/Shell, AWS, Azure, GCP, Cloud (any), Kubernetes, CI/CD, Git, Monitoring, Automation, Troubleshooting</t>
   </si>
   <si>
@@ -199,6 +220,24 @@
     <t xml:space="preserve">2026-08-20</t>
   </si>
   <si>
+    <t xml:space="preserve">Linux &amp; HPC Systems Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Novocure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tirat HaCarmel, Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Docker, Kubernetes, CI/CD, Git, Terraform/IaC, Networking, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/linux-hpc-systems-engineer-at-novocure-4478872342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-15</t>
+  </si>
+  <si>
     <t xml:space="preserve">System Engineer</t>
   </si>
   <si>
@@ -265,6 +304,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-at-cross-river-4478788112</t>
   </si>
   <si>
+    <t xml:space="preserve">HPC Operations Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NVIDIA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Terraform/IaC, Networking, Monitoring, Active Directory, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cloud Monitoring Engineer (Student Position)</t>
   </si>
   <si>
@@ -298,6 +352,15 @@
     <t xml:space="preserve">2026-08-18</t>
   </si>
   <si>
+    <t xml:space="preserve">Security Analyst (Student Position)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Cloud (any), Docker, Kubernetes, Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/security-analyst-student-position-at-upwind-security-4473525994</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Engineer Student, SPIV team</t>
   </si>
   <si>
@@ -331,252 +394,282 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
-    <t xml:space="preserve">System Administrator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Medulla</t>
+    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kela Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Haifa District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Support Engineer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, AWS, Azure, Cloud (any), Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-cye-4477476916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OnCloud</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Software Engineering INTERN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Microsoft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineering-intern-at-microsoft-4451071541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raft Technologies</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Python, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IT Service Desk Team Leader</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Appsflyer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Herzliya</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gini-Apps</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (1006801)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Elad Software Systems</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-1006801-at-elad-software-systems-4479783873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Junior System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hozek Technologies Ltd.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure, Cloud (any), Virtualization, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
     <t xml:space="preserve">Netanya, Center District, Israel</t>
   </si>
   <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Azure, Cloud (any), Networking, Active Directory, Windows Server</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-medulla-4468207460</t>
+    <t xml:space="preserve">Python, CI/CD, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-at-fetcherr-4449296509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">evoke</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">NOC Operator (37577)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Gongio</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Taboola</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Budapest, Hungary</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
   </si>
   <si>
     <t xml:space="preserve">2026-10-14</t>
   </si>
   <si>
-    <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kela Technologies</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Bash/Shell, Docker, Kubernetes, Networking, Monitoring, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/support-engineer-noc-tier-1-at-kela-technologies-4461059776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-31</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior CAD Engineer, University Graduate, Google Cloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Haifa District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, GCP, Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cad-engineer-university-graduate-google-cloud-at-google-4475452638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobgether</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Python, Cloud (any), Kubernetes, Networking, Monitoring, Databases, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/technical-support-engineer-at-jobgether-4477100901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CONTROP Precision Technologies Ltd.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kfar Saba, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, AWS, Azure, Cloud (any), Networking, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-controp-precision-technologies-ltd-4460943847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-02</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Junior Cloud Security Engineer (Entry-Level)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OnCloud</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-cloud-security-engineer-entry-level-at-oncloud-4456904380</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-26</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SPD Hosting LTD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Rishon LeZion, Center District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Bash/Shell, Networking, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-spd-hosting-ltd-4476095499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">IT Service Desk Team Leader</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Appsflyer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Bash/Shell, Cloud (any), Networking, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-07</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gini-Apps</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python, Networking, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-gini-apps-4440026223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (24/7 Shift-Based)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">evoke</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Herzliya, Tel Aviv District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-24-7-shift-based-at-evoke-4462157700</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-10-12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-abra-4413899531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-19</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring Technical Support Specialist (NOC)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SuperCom (NASDAQ: SPCB)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS, Cloud (any), Networking, Monitoring, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/monitoring-technical-support-specialist-noc-at-supercom-nasdaq-spcb-4465838312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-11</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Gongio</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell, Monitoring, Automation, Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/gongio/jobs/4713260006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-09-29</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Technical Support Engineer- Tier 3</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Taboola</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Budapest, Hungary</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD, Monitoring, Databases, Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.taboola.com/careers/job/8176664?gh_jid=8176664</t>
-  </si>
-  <si>
     <t xml:space="preserve">Data Center IT Technician - Beit Shemesh</t>
   </si>
   <si>
@@ -589,7 +682,16 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/data-center-it-technician-beit-shemesh-at-nebius-4437673265</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-08-14</t>
+    <t xml:space="preserve">Software Engineer – Graduate Program (Bootcamp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Palo Alto Networks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-%E2%80%93-graduate-program-bootcamp-at-palo-alto-networks-4476680286</t>
   </si>
   <si>
     <t xml:space="preserve">Sela</t>
@@ -619,9 +721,6 @@
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
-    <t xml:space="preserve">Petah Tikva, Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4477961931</t>
   </si>
   <si>
@@ -637,6 +736,21 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
   </si>
   <si>
+    <t xml:space="preserve">Recovery Analyst Student</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Forter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Israel - Tel Aviv</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cloud (any), Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8887212002</t>
+  </si>
+  <si>
     <t xml:space="preserve">NOC Engineer- Student Position</t>
   </si>
   <si>
@@ -700,157 +814,145 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Raft Technologies</t>
+    <t xml:space="preserve">Student Success Coach</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FindTutors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">London, London, England, United Kingdom</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-05</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Skill</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Roles requiring it</t>
+  </si>
+  <si>
+    <t xml:space="preserve">What to learn / where to start</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Monitoring</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Networking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Docker</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Kubernetes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Azure</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CI/CD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Terraform/IaC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GCP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Count</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pivot path advice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jobs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">OK</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Error</t>
   </si>
   <si>
     <t xml:space="preserve">yes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-raft-technologies-4433796227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HPC Operations Engineer</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NVIDIA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Yokneam Ilit, North District, Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/hpc-operations-engineer-at-nvidia-4471977303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Skill</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Roles requiring it</t>
-  </si>
-  <si>
-    <t xml:space="preserve">What to learn / where to start</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Troubleshooting</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Practice with TryHackMe + read SRE Workbook ch 12</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Monitoring</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Prometheus + Grafana docs, deploy on minikube</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Networking</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Kubernetes</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Azure</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AZ-900 Fundamentals → AZ-104 path on MS Learn (free)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Docker</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
-  </si>
-  <si>
-    <t xml:space="preserve">CI/CD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: GitHub Actions docs + practice on a personal repo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">GCP</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Google Cloud Skills Boost (free) → ACE cert</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Terraform/IaC</t>
-  </si>
-  <si>
-    <t xml:space="preserve">HashiCorp Learn (free) + build a 3-tier app on AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Count</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Pivot path advice</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Jobs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">OK</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Error</t>
   </si>
 </sst>
 </file>
@@ -975,7 +1077,7 @@
         <v>6</v>
       </c>
       <c r="B6" s="3">
-        <v>38</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7">
@@ -983,7 +1085,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8">
@@ -999,7 +1101,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>341</v>
+        <v>336</v>
       </c>
     </row>
     <row r="10">
@@ -1081,7 +1183,7 @@
         <v>25</v>
       </c>
       <c r="B21" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="22">
@@ -1089,7 +1191,7 @@
         <v>26</v>
       </c>
       <c r="B22" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -1097,7 +1199,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24">
@@ -1109,36 +1211,52 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3"/>
-      <c r="B25" s="3"/>
+      <c r="A25" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B25" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B26" s="3"/>
+        <v>30</v>
+      </c>
+      <c r="B26" s="3">
+        <v>1</v>
+      </c>
     </row>
     <row r="27">
-      <c r="A27" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B27" s="3">
-        <v>29</v>
-      </c>
+      <c r="A27" s="3"/>
+      <c r="B27" s="3"/>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B28" s="3">
-        <v>7</v>
-      </c>
+      <c r="B28" s="3"/>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="B29" s="3">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B30" s="3">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B31" s="3">
         <v>2</v>
       </c>
     </row>
@@ -1151,7 +1269,7 @@
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="56" customWidth="1"/>
-    <col min="3" max="3" width="37" customWidth="1"/>
+    <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
     <col min="6" max="6" width="16" customWidth="1"/>
@@ -1163,34 +1281,34 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
@@ -1198,31 +1316,31 @@
         <v>1</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
     </row>
     <row r="3">
@@ -1230,13 +1348,13 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>25</v>
@@ -1245,16 +1363,16 @@
         <v>100</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4">
@@ -1262,31 +1380,31 @@
         <v>3</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5">
@@ -1294,13 +1412,13 @@
         <v>4</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>25</v>
@@ -1309,16 +1427,16 @@
         <v>100</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6">
@@ -1326,31 +1444,31 @@
         <v>5</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F6" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7">
@@ -1358,31 +1476,31 @@
         <v>6</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F7" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8">
@@ -1390,31 +1508,31 @@
         <v>7</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F8" s="3">
+        <v>96</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>84</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="9">
@@ -1422,31 +1540,31 @@
         <v>8</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F9" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
     </row>
     <row r="10">
@@ -1454,31 +1572,31 @@
         <v>9</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F10" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
     </row>
     <row r="11">
@@ -1486,31 +1604,31 @@
         <v>10</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F11" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
     </row>
     <row r="12">
@@ -1518,31 +1636,31 @@
         <v>11</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F12" s="3">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
     </row>
     <row r="13">
@@ -1550,31 +1668,31 @@
         <v>12</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D13" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F13" s="3">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="14">
@@ -1582,31 +1700,31 @@
         <v>13</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="F14" s="3">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="G14" s="3" t="s">
         <v>113</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
     </row>
     <row r="15">
@@ -1614,31 +1732,31 @@
         <v>14</v>
       </c>
       <c r="B15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="F15" s="3">
+        <v>70</v>
+      </c>
+      <c r="G15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="F15" s="3">
-        <v>57</v>
-      </c>
-      <c r="G15" s="3" t="s">
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
     </row>
     <row r="16">
@@ -1646,31 +1764,31 @@
         <v>15</v>
       </c>
       <c r="B16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="C16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="E16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="3">
+        <v>68</v>
+      </c>
+      <c r="G16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="E16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="F16" s="3">
-        <v>51</v>
-      </c>
-      <c r="G16" s="3" t="s">
+      <c r="H16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>125</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="17">
@@ -1678,25 +1796,25 @@
         <v>16</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F17" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="G17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>129</v>
@@ -1722,19 +1840,19 @@
         <v>28</v>
       </c>
       <c r="F18" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
     </row>
     <row r="19">
@@ -1742,7 +1860,7 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>137</v>
@@ -1751,22 +1869,22 @@
         <v>138</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F19" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="G19" s="3" t="s">
         <v>139</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
     </row>
     <row r="20">
@@ -1774,31 +1892,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="F20" s="3">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21">
@@ -1806,31 +1924,31 @@
         <v>20</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
     </row>
     <row r="22">
@@ -1838,31 +1956,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="E22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F22" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
     </row>
     <row r="23">
@@ -1870,31 +1988,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F23" s="3">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
     </row>
     <row r="24">
@@ -1902,31 +2020,31 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="E24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F24" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
     </row>
     <row r="25">
@@ -1934,31 +2052,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
     </row>
     <row r="26">
@@ -1966,31 +2084,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="F26" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>
@@ -2029,7 +2147,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="37" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2043,83 +2161,83 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>25</v>
@@ -2128,68 +2246,68 @@
         <v>100</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>28</v>
+        <v>29</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H4" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I4" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>55</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>25</v>
@@ -2198,433 +2316,433 @@
         <v>100</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>14</v>
+        <v>56</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E6" s="3">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H6" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I6" s="3" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="J6" s="3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E7" s="3">
-        <v>88</v>
+        <v>100</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H7" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I7" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D8" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E8" s="3">
+        <v>96</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="G8" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I8" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="F8" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="G8" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H8" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I8" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="J8" s="3" t="s">
-        <v>48</v>
-      </c>
       <c r="K8" s="3">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E9" s="3">
-        <v>83</v>
+        <v>88</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H9" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I9" s="3" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="K9" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>57</v>
+        <v>93</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E10" s="3">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="J10" s="3" t="s">
-        <v>93</v>
+        <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>57</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E11" s="3">
-        <v>70</v>
+        <v>84</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="J11" s="3" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="K11" s="3">
-        <v>55</v>
+        <v>15</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E12" s="3">
-        <v>68</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H12" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I12" s="3" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="J12" s="3" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="K12" s="3">
-        <v>40</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>107</v>
+        <v>59</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E13" s="3">
-        <v>64</v>
+        <v>80</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H13" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I13" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="J13" s="3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>0</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>57</v>
+        <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E14" s="3">
-        <v>61</v>
+        <v>74</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H14" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>114</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>115</v>
+        <v>78</v>
       </c>
       <c r="K14" s="3">
-        <v>44</v>
+        <v>15</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="C15" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="D15" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="3">
+        <v>70</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="E15" s="3">
-        <v>57</v>
-      </c>
-      <c r="F15" s="3" t="s">
+      <c r="G15" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H15" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I15" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="G15" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H15" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I15" s="3" t="s">
-        <v>120</v>
-      </c>
       <c r="J15" s="3" t="s">
-        <v>88</v>
+        <v>67</v>
       </c>
       <c r="K15" s="3">
-        <v>6</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="C16" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="C16" s="3" t="s">
+      <c r="D16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="3">
+        <v>68</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="3">
-        <v>51</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="G16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H16" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I16" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="G16" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H16" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="3" t="s">
+      <c r="J16" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="J16" s="3" t="s">
-        <v>110</v>
-      </c>
       <c r="K16" s="3">
-        <v>0</v>
+        <v>41</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>105</v>
+        <v>126</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>127</v>
+        <v>59</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E17" s="3">
-        <v>48</v>
+        <v>61</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>128</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I17" s="3" t="s">
         <v>129</v>
@@ -2633,7 +2751,7 @@
         <v>130</v>
       </c>
       <c r="K17" s="3">
-        <v>42</v>
+        <v>45</v>
       </c>
     </row>
     <row r="18">
@@ -2650,30 +2768,30 @@
         <v>28</v>
       </c>
       <c r="E18" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>134</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H18" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
         <v>135</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>136</v>
+        <v>106</v>
       </c>
       <c r="K18" s="3">
-        <v>49</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>137</v>
@@ -2682,200 +2800,200 @@
         <v>138</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E19" s="3">
-        <v>36</v>
+        <v>54</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>139</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H19" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
         <v>140</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>48</v>
+        <v>141</v>
       </c>
       <c r="K19" s="3">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E20" s="3">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H20" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="K20" s="3">
-        <v>7</v>
+        <v>50</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H21" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I21" s="3" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>60</v>
+        <v>67</v>
       </c>
       <c r="K21" s="3">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>153</v>
+        <v>59</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E22" s="3">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H22" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>130</v>
+        <v>157</v>
       </c>
       <c r="K22" s="3">
-        <v>42</v>
+        <v>3</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>133</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E23" s="3">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="K23" s="3">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>133</v>
+        <v>59</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E24" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H24" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="J24" s="3" t="s">
-        <v>164</v>
+        <v>67</v>
       </c>
       <c r="K24" s="3">
         <v>56</v>
@@ -2883,77 +3001,77 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>57</v>
+        <v>169</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H25" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>169</v>
+        <v>73</v>
       </c>
       <c r="K25" s="3">
-        <v>33</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="E26" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>175</v>
+        <v>90</v>
       </c>
       <c r="K26" s="3">
-        <v>15</v>
+        <v>10</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>182</v>
+        <v>136</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>183</v>
@@ -2962,235 +3080,235 @@
         <v>184</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E27" s="3">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>185</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H27" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
         <v>186</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>110</v>
+        <v>187</v>
       </c>
       <c r="K27" s="3">
-        <v>0</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>123</v>
+        <v>138</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H28" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="K28" s="3">
-        <v>61</v>
+        <v>43</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>66</v>
+        <v>193</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E29" s="3">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>48</v>
+        <v>157</v>
       </c>
       <c r="K29" s="3">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>195</v>
+        <v>153</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E30" s="3">
-        <v>12</v>
+        <v>24</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="K30" s="3">
-        <v>8</v>
+        <v>57</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>201</v>
+        <v>59</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E31" s="3">
-        <v>12</v>
+        <v>23</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H31" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>48</v>
+        <v>205</v>
       </c>
       <c r="K31" s="3">
-        <v>1</v>
+        <v>34</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>123</v>
+        <v>208</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E32" s="3">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="G32" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H32" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I32" s="3" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>191</v>
+        <v>211</v>
       </c>
       <c r="K32" s="3">
-        <v>61</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
-        <v>207</v>
+        <v>212</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>208</v>
+        <v>213</v>
       </c>
       <c r="C33" s="3" t="s">
-        <v>201</v>
+        <v>214</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E33" s="3">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="G33" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H33" s="3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="I33" s="3" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="J33" s="3" t="s">
-        <v>48</v>
+        <v>217</v>
       </c>
       <c r="K33" s="3">
         <v>1</v>
@@ -3198,208 +3316,422 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>211</v>
+        <v>218</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>212</v>
+        <v>219</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>213</v>
+        <v>150</v>
       </c>
       <c r="D34" s="3" t="s">
         <v>27</v>
       </c>
       <c r="E34" s="3">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="G34" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H34" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I34" s="3" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="J34" s="3" t="s">
-        <v>216</v>
+        <v>187</v>
       </c>
       <c r="K34" s="3">
-        <v>13</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>217</v>
+        <v>222</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>218</v>
+        <v>223</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>219</v>
+        <v>174</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>4</v>
+        <v>17</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H35" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>222</v>
+        <v>73</v>
       </c>
       <c r="K35" s="3">
-        <v>34</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>223</v>
+        <v>79</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>225</v>
+        <v>144</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E36" s="3">
-        <v>0</v>
-      </c>
-      <c r="F36" s="3"/>
+        <v>16</v>
+      </c>
+      <c r="F36" s="3" t="s">
+        <v>227</v>
+      </c>
       <c r="G36" s="3" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="H36" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>227</v>
+        <v>50</v>
       </c>
       <c r="K36" s="3">
-        <v>77</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>147</v>
+        <v>229</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>57</v>
+        <v>144</v>
       </c>
       <c r="D37" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E37" s="3">
-        <v>0</v>
-      </c>
-      <c r="F37" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F37" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="G37" s="3" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="H37" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>160</v>
+        <v>233</v>
       </c>
       <c r="K37" s="3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>231</v>
+        <v>153</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>233</v>
+        <v>174</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>0</v>
-      </c>
-      <c r="F38" s="3"/>
+        <v>12</v>
+      </c>
+      <c r="F38" s="3" t="s">
+        <v>231</v>
+      </c>
       <c r="G38" s="3" t="s">
-        <v>229</v>
+        <v>182</v>
       </c>
       <c r="H38" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="J38" s="3" t="s">
-        <v>65</v>
+        <v>50</v>
       </c>
       <c r="K38" s="3">
-        <v>14</v>
+        <v>2</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>237</v>
+        <v>150</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E39" s="3">
+        <v>12</v>
+      </c>
+      <c r="F39" s="3" t="s">
+        <v>238</v>
+      </c>
+      <c r="G39" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H39" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I39" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="J39" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="K39" s="3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C40" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="D40" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E40" s="3">
+        <v>8</v>
+      </c>
+      <c r="F40" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="G40" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H40" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I40" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="J40" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K40" s="3">
         <v>0</v>
       </c>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="H39" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I39" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="J39" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="K39" s="3">
-        <v>70</v>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="C41" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D41" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E41" s="3">
+        <v>8</v>
+      </c>
+      <c r="F41" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="G41" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H41" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I41" s="3" t="s">
+        <v>248</v>
+      </c>
+      <c r="J41" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="K41" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="3" t="s">
+        <v>249</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>250</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E42" s="3">
+        <v>4</v>
+      </c>
+      <c r="F42" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="G42" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H42" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I42" s="3" t="s">
+        <v>253</v>
+      </c>
+      <c r="J42" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="K42" s="3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>256</v>
+      </c>
+      <c r="C43" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="D43" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E43" s="3">
+        <v>4</v>
+      </c>
+      <c r="F43" s="3" t="s">
+        <v>258</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I43" s="3" t="s">
+        <v>259</v>
+      </c>
+      <c r="J43" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="K43" s="3">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="3" t="s">
+        <v>261</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="C44" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="D44" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E44" s="3">
+        <v>0</v>
+      </c>
+      <c r="F44" s="3"/>
+      <c r="G44" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H44" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I44" s="3" t="s">
+        <v>264</v>
+      </c>
+      <c r="J44" s="3" t="s">
+        <v>265</v>
+      </c>
+      <c r="K44" s="3">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="3" t="s">
+        <v>266</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>267</v>
+      </c>
+      <c r="C45" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="D45" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E45" s="3">
+        <v>0</v>
+      </c>
+      <c r="F45" s="3"/>
+      <c r="G45" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>269</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>270</v>
+      </c>
+      <c r="K45" s="3">
+        <v>71</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:K39"/>
+  <autoFilter ref="A1:K45"/>
   <hyperlinks>
     <hyperlink ref="I2" r:id="rId1"/>
     <hyperlink ref="I3" r:id="rId2"/>
@@ -3439,6 +3771,12 @@
     <hyperlink ref="I37" r:id="rId36"/>
     <hyperlink ref="I38" r:id="rId37"/>
     <hyperlink ref="I39" r:id="rId38"/>
+    <hyperlink ref="I40" r:id="rId39"/>
+    <hyperlink ref="I41" r:id="rId40"/>
+    <hyperlink ref="I42" r:id="rId41"/>
+    <hyperlink ref="I43" r:id="rId42"/>
+    <hyperlink ref="I44" r:id="rId43"/>
+    <hyperlink ref="I45" r:id="rId44"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3446,9 +3784,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="1" max="1" width="49" customWidth="1"/>
+    <col min="2" max="2" width="23" customWidth="1"/>
+    <col min="3" max="3" width="25" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3457,102 +3795,126 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>105</v>
+        <v>68</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>106</v>
+        <v>69</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>64</v>
+        <v>100</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>108</v>
+        <v>71</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>109</v>
+        <v>72</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>121</v>
+        <v>167</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>122</v>
+        <v>168</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3">
-        <v>51</v>
+        <v>28</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>124</v>
+        <v>170</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>125</v>
+        <v>171</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>182</v>
+        <v>222</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>183</v>
+        <v>223</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>26</v>
       </c>
       <c r="D4" s="3">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>185</v>
+        <v>224</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>186</v>
+        <v>225</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>110</v>
+        <v>73</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="s">
+        <v>240</v>
+      </c>
+      <c r="B5" s="3" t="s">
+        <v>241</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D5" s="3">
+        <v>8</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="F5" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="G5" s="3" t="s">
+        <v>73</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G4"/>
+  <autoFilter ref="A1:G5"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
+    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3567,178 +3929,178 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>240</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>241</v>
+        <v>272</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>242</v>
+        <v>273</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>205</v>
+        <v>274</v>
       </c>
       <c r="B2" s="3">
-        <v>20</v>
+        <v>28</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>243</v>
+        <v>275</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>244</v>
+        <v>276</v>
       </c>
       <c r="B3" s="3">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>245</v>
+        <v>277</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="B4" s="3">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>247</v>
+        <v>278</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B5" s="3">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>249</v>
+        <v>279</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>214</v>
+        <v>280</v>
       </c>
       <c r="B6" s="3">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>250</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>220</v>
+        <v>258</v>
       </c>
       <c r="B7" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>251</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>252</v>
+        <v>283</v>
       </c>
       <c r="B8" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>253</v>
+        <v>284</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>254</v>
+        <v>285</v>
       </c>
       <c r="B9" s="3">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>255</v>
+        <v>286</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>256</v>
+        <v>287</v>
       </c>
       <c r="B10" s="3">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>257</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>258</v>
+        <v>289</v>
       </c>
       <c r="B11" s="3">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>259</v>
+        <v>290</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>260</v>
+        <v>291</v>
       </c>
       <c r="B12" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>261</v>
+        <v>292</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>262</v>
+        <v>293</v>
       </c>
       <c r="B13" s="3">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>263</v>
+        <v>294</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>264</v>
+        <v>295</v>
       </c>
       <c r="B14" s="3">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>265</v>
+        <v>296</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>266</v>
+        <v>297</v>
       </c>
       <c r="B15" s="3">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>267</v>
+        <v>298</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>268</v>
+        <v>299</v>
       </c>
       <c r="B16" s="3">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>269</v>
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -3755,13 +4117,13 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>270</v>
+        <v>301</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>271</v>
+        <v>302</v>
       </c>
     </row>
     <row r="2">
@@ -3769,10 +4131,10 @@
         <v>25</v>
       </c>
       <c r="B2" s="3">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>272</v>
+        <v>303</v>
       </c>
     </row>
     <row r="3">
@@ -3780,10 +4142,10 @@
         <v>26</v>
       </c>
       <c r="B3" s="3">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>273</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4">
@@ -3791,10 +4153,10 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>274</v>
+        <v>305</v>
       </c>
     </row>
     <row r="5">
@@ -3805,7 +4167,29 @@
         <v>3</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>275</v>
+        <v>306</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="3">
+        <v>1</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B7" s="3">
+        <v>1</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>308</v>
       </c>
     </row>
   </sheetData>
@@ -3823,51 +4207,51 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>276</v>
+        <v>309</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>277</v>
+        <v>310</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>278</v>
+        <v>311</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="D2" s="3"/>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>31</v>
+        <v>36</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="D3" s="3"/>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B4" s="3">
         <v>2</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>229</v>
+        <v>312</v>
       </c>
       <c r="D4" s="3"/>
     </row>

--- a/reports/devops-juniors-israel-2026-W42.xlsx
+++ b/reports/devops-juniors-israel-2026-W42.xlsx
@@ -31,7 +31,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-15T11:19:53</t>
+    <t xml:space="preserve">2026-10-16T11:15:08</t>
   </si>
   <si>
     <t xml:space="preserve">Total junior-pipeline matches</t>
@@ -94,21 +94,21 @@
     <t xml:space="preserve">SysAdmin / NOC</t>
   </si>
   <si>
+    <t xml:space="preserve">Help Desk / IT Support</t>
+  </si>
+  <si>
     <t xml:space="preserve">Trainee / Bootcamp Grad</t>
   </si>
   <si>
-    <t xml:space="preserve">Help Desk / IT Support</t>
-  </si>
-  <si>
     <t xml:space="preserve">Junior SRE / Cloud / Platform</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior DevOps</t>
+  </si>
+  <si>
     <t xml:space="preserve">Junior SysAdmin / Linux</t>
   </si>
   <si>
-    <t xml:space="preserve">Junior DevOps</t>
-  </si>
-  <si>
     <t xml:space="preserve">By source</t>
   </si>
   <si>
@@ -376,6 +376,24 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/software-engineer-student-spiv-team-at-amazon-4456348779</t>
   </si>
   <si>
+    <t xml:space="preserve">Student Software Engineer – Cloud, Big Data, Billing &amp; AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SAP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Raanana, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, Cloud (any), Docker, Kubernetes, CI/CD, Monitoring, Automation, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/student-software-engineer-%E2%80%93-cloud-big-data-billing-ai-at-sap-4476596020</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-07</t>
+  </si>
+  <si>
     <t xml:space="preserve">Production Operations Engineer</t>
   </si>
   <si>
@@ -394,6 +412,24 @@
     <t xml:space="preserve">2026-09-04</t>
   </si>
   <si>
+    <t xml:space="preserve">System Administrator</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abra</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux, Bash/Shell, AWS, Azure, Cloud (any), Networking, Active Directory, Windows Server, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/system-administrator-at-abra-4467537853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-16</t>
+  </si>
+  <si>
     <t xml:space="preserve">Support Engineer (NOC / Tier 1)</t>
   </si>
   <si>
@@ -448,9 +484,6 @@
     <t xml:space="preserve">OnCloud</t>
   </si>
   <si>
-    <t xml:space="preserve">Center District, Israel</t>
-  </si>
-  <si>
     <t xml:space="preserve">Bash/Shell, Azure, Cloud (any), Networking, Active Directory</t>
   </si>
   <si>
@@ -460,6 +493,21 @@
     <t xml:space="preserve">2026-08-26</t>
   </si>
   <si>
+    <t xml:space="preserve">Junior Developer, Core Platform</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AppCard, Inc.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hod HaSharon, Center District, Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Python, AWS, Databases, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-developer-core-platform-at-appcard-inc-4477317181</t>
+  </si>
+  <si>
     <t xml:space="preserve">Software Engineering INTERN</t>
   </si>
   <si>
@@ -505,7 +553,22 @@
     <t xml:space="preserve">https://careers.appsflyer.com/jobs/position/8874236002?gh_jid=8874236002</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-07</t>
+    <t xml:space="preserve">Title</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Stack</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Needs JD Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">URL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Days Open</t>
+  </si>
+  <si>
+    <t xml:space="preserve">no</t>
   </si>
   <si>
     <t xml:space="preserve">Gini-Apps</t>
@@ -547,24 +610,6 @@
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/junior-system-administrator-at-hozek-technologies-ltd-4473634499</t>
   </si>
   <si>
-    <t xml:space="preserve">Title</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Stack</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Needs JD Review</t>
-  </si>
-  <si>
-    <t xml:space="preserve">URL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Days Open</t>
-  </si>
-  <si>
-    <t xml:space="preserve">no</t>
-  </si>
-  <si>
     <t xml:space="preserve">Fetcherr</t>
   </si>
   <si>
@@ -595,21 +640,6 @@
     <t xml:space="preserve">2026-09-02</t>
   </si>
   <si>
-    <t xml:space="preserve">NOC Operator (37577)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">מרטנס | Mertens – מקבוצת מלם תים</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux, Networking, Monitoring, Virtualization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-37577-at-%D7%9E%D7%A8%D7%98%D7%A0%D7%A1-mertens-%E2%80%93-%D7%9E%D7%A7%D7%91%D7%95%D7%A6%D7%AA-%D7%9E%D7%9C%D7%9D-%D7%AA%D7%99%D7%9D-4478398856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">abra</t>
-  </si>
-  <si>
     <t xml:space="preserve">Linux, Monitoring, Windows Server, Troubleshooting</t>
   </si>
   <si>
@@ -718,37 +748,25 @@
     <t xml:space="preserve">2026-10-06</t>
   </si>
   <si>
+    <t xml:space="preserve">NOC Israel</t>
+  </si>
+  <si>
+    <t xml:space="preserve">WaveBL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Linux</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tata Consultancy Services</t>
   </si>
   <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4477961931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">NOC Israel</t>
-  </si>
-  <si>
-    <t xml:space="preserve">WaveBL</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Linux</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc%0A%09%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%0A%09%09%09%09%09%09%09%09%09%09israel-at-wavebl-4443917908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Recovery Analyst Student</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Forter</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Israel - Tel Aviv</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Cloud (any), Automation</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://job-boards.greenhouse.io/forter/jobs/8887212002</t>
+    <t xml:space="preserve">Monitoring, Troubleshooting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-operator-at-tata-consultancy-services-4479110861</t>
   </si>
   <si>
     <t xml:space="preserve">NOC Engineer- Student Position</t>
@@ -757,9 +775,6 @@
     <t xml:space="preserve">Global-e</t>
   </si>
   <si>
-    <t xml:space="preserve">Monitoring, Troubleshooting</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://il.linkedin.com/jobs/view/noc-engineer-student-position-at-global-e-4478768786</t>
   </si>
   <si>
@@ -814,21 +829,6 @@
     <t xml:space="preserve">2026-07-29</t>
   </si>
   <si>
-    <t xml:space="preserve">Student Success Coach</t>
-  </si>
-  <si>
-    <t xml:space="preserve">FindTutors</t>
-  </si>
-  <si>
-    <t xml:space="preserve">London, London, England, United Kingdom</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://remoteOK.com/remote-jobs/remote-student-success-coach-findtutors-1136086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2026-08-05</t>
-  </si>
-  <si>
     <t xml:space="preserve">Skill</t>
   </si>
   <si>
@@ -853,13 +853,19 @@
     <t xml:space="preserve">Pick one cloud, study free fundamentals first</t>
   </si>
   <si>
+    <t xml:space="preserve">Python</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+  </si>
+  <si>
     <t xml:space="preserve">Free: linuxjourney.com + 'The Linux Command Line' book</t>
   </si>
   <si>
-    <t xml:space="preserve">Python</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Automate the Boring Stuff (free book) + python.org tutorial</t>
+    <t xml:space="preserve">Bash/Shell</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
   </si>
   <si>
     <t xml:space="preserve">Start with Python + Bash; build 3 small home-lab automations</t>
@@ -871,30 +877,24 @@
     <t xml:space="preserve">Cisco Packet Tracer (free) + study CCNA blueprint</t>
   </si>
   <si>
-    <t xml:space="preserve">Bash/Shell</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Free: linuxjourney.com + try OverTheWire bandit wargame</t>
-  </si>
-  <si>
     <t xml:space="preserve">Docker</t>
   </si>
   <si>
     <t xml:space="preserve">Free Docker Get Started tutorial + build 3 home-lab containers</t>
   </si>
   <si>
+    <t xml:space="preserve">AWS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
+  </si>
+  <si>
     <t xml:space="preserve">Kubernetes</t>
   </si>
   <si>
     <t xml:space="preserve">kubernetes.io tutorials → minikube on laptop → KCNA cert</t>
   </si>
   <si>
-    <t xml:space="preserve">AWS</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AWS Skill Builder (free) → SAA-C03 cert (~$150 exam)</t>
-  </si>
-  <si>
     <t xml:space="preserve">Azure</t>
   </si>
   <si>
@@ -928,19 +928,19 @@
     <t xml:space="preserve">Already in IT — strengthen Linux + automation → apply to DevOps in 12-18mo.</t>
   </si>
   <si>
+    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
+  </si>
+  <si>
     <t xml:space="preserve">Cyclical — surge after bootcamp graduations (Aug/Feb).</t>
   </si>
   <si>
-    <t xml:space="preserve">Tier 1/2 → SysAdmin → Junior DevOps. ~24 month path.</t>
-  </si>
-  <si>
     <t xml:space="preserve">Often paired with on-call. Strong learning track.</t>
   </si>
   <si>
+    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
+  </si>
+  <si>
     <t xml:space="preserve">12-18 months → Junior DevOps. Strengthen Linux + Python + AWS.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Direct DevOps role — apply aggressively. Rare and competitive.</t>
   </si>
   <si>
     <t xml:space="preserve">Jobs</t>
@@ -1085,7 +1085,7 @@
         <v>7</v>
       </c>
       <c r="B7" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -1093,7 +1093,7 @@
         <v>8</v>
       </c>
       <c r="B8" s="3">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="9">
@@ -1101,7 +1101,7 @@
         <v>9</v>
       </c>
       <c r="B9" s="3">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="10">
@@ -1199,7 +1199,7 @@
         <v>27</v>
       </c>
       <c r="B23" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="24">
@@ -1207,7 +1207,7 @@
         <v>28</v>
       </c>
       <c r="B24" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="25">
@@ -1241,7 +1241,7 @@
         <v>32</v>
       </c>
       <c r="B29" s="3">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="30">
@@ -1249,7 +1249,7 @@
         <v>33</v>
       </c>
       <c r="B30" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31">
@@ -1257,7 +1257,7 @@
         <v>34</v>
       </c>
       <c r="B31" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -1268,7 +1268,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
-    <col min="2" max="2" width="56" customWidth="1"/>
+    <col min="2" max="2" width="59" customWidth="1"/>
     <col min="3" max="3" width="32" customWidth="1"/>
     <col min="4" max="4" width="44" customWidth="1"/>
     <col min="5" max="5" width="31" customWidth="1"/>
@@ -1325,7 +1325,7 @@
         <v>47</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F2" s="3">
         <v>100</v>
@@ -1389,7 +1389,7 @@
         <v>59</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="F4" s="3">
         <v>100</v>
@@ -1645,7 +1645,7 @@
         <v>103</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F12" s="3">
         <v>83</v>
@@ -1709,7 +1709,7 @@
         <v>103</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" s="3">
         <v>74</v>
@@ -1741,7 +1741,7 @@
         <v>117</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F15" s="3">
         <v>70</v>
@@ -1773,16 +1773,16 @@
         <v>122</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F16" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>123</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>124</v>
@@ -1802,25 +1802,25 @@
         <v>127</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F17" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="18">
@@ -1828,31 +1828,31 @@
         <v>17</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="F18" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
     </row>
     <row r="19">
@@ -1860,31 +1860,31 @@
         <v>18</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="F19" s="3">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="20">
@@ -1892,31 +1892,31 @@
         <v>19</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E20" s="3" t="s">
         <v>28</v>
       </c>
       <c r="F20" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
     </row>
     <row r="21">
@@ -1936,7 +1936,7 @@
         <v>26</v>
       </c>
       <c r="F21" s="3">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="G21" s="3" t="s">
         <v>151</v>
@@ -1948,7 +1948,7 @@
         <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
@@ -1956,31 +1956,31 @@
         <v>21</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="F22" s="3">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
     </row>
     <row r="23">
@@ -1988,31 +1988,31 @@
         <v>22</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F23" s="3">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24">
@@ -2020,28 +2020,28 @@
         <v>23</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="F24" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>67</v>
@@ -2052,31 +2052,31 @@
         <v>24</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="F25" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
     </row>
     <row r="26">
@@ -2084,31 +2084,31 @@
         <v>25</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F26" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
     </row>
   </sheetData>
@@ -2146,8 +2146,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="56" customWidth="1"/>
-    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="1" max="1" width="59" customWidth="1"/>
+    <col min="2" max="2" width="32" customWidth="1"/>
     <col min="3" max="3" width="44" customWidth="1"/>
     <col min="4" max="4" width="31" customWidth="1"/>
     <col min="5" max="5" width="16" customWidth="1"/>
@@ -2161,7 +2161,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>37</v>
@@ -2176,22 +2176,22 @@
         <v>40</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="H1" s="1" t="s">
         <v>42</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J1" s="1" t="s">
         <v>44</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="2">
@@ -2205,7 +2205,7 @@
         <v>47</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" s="3">
         <v>100</v>
@@ -2214,7 +2214,7 @@
         <v>48</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H2" s="3" t="s">
         <v>33</v>
@@ -2226,7 +2226,7 @@
         <v>50</v>
       </c>
       <c r="K2" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -2249,7 +2249,7 @@
         <v>54</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H3" s="3" t="s">
         <v>32</v>
@@ -2261,7 +2261,7 @@
         <v>56</v>
       </c>
       <c r="K3" s="3">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
@@ -2275,7 +2275,7 @@
         <v>59</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E4" s="3">
         <v>100</v>
@@ -2284,7 +2284,7 @@
         <v>60</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H4" s="3" t="s">
         <v>32</v>
@@ -2296,7 +2296,7 @@
         <v>62</v>
       </c>
       <c r="K4" s="3">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
@@ -2319,7 +2319,7 @@
         <v>65</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H5" s="3" t="s">
         <v>32</v>
@@ -2331,7 +2331,7 @@
         <v>67</v>
       </c>
       <c r="K5" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6">
@@ -2354,7 +2354,7 @@
         <v>71</v>
       </c>
       <c r="G6" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H6" s="3" t="s">
         <v>32</v>
@@ -2366,7 +2366,7 @@
         <v>73</v>
       </c>
       <c r="K6" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -2389,7 +2389,7 @@
         <v>76</v>
       </c>
       <c r="G7" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H7" s="3" t="s">
         <v>32</v>
@@ -2401,7 +2401,7 @@
         <v>78</v>
       </c>
       <c r="K7" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8">
@@ -2424,7 +2424,7 @@
         <v>82</v>
       </c>
       <c r="G8" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H8" s="3" t="s">
         <v>32</v>
@@ -2436,7 +2436,7 @@
         <v>84</v>
       </c>
       <c r="K8" s="3">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9">
@@ -2459,7 +2459,7 @@
         <v>88</v>
       </c>
       <c r="G9" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H9" s="3" t="s">
         <v>32</v>
@@ -2471,7 +2471,7 @@
         <v>90</v>
       </c>
       <c r="K9" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10">
@@ -2494,7 +2494,7 @@
         <v>94</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H10" s="3" t="s">
         <v>32</v>
@@ -2506,7 +2506,7 @@
         <v>50</v>
       </c>
       <c r="K10" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11">
@@ -2529,7 +2529,7 @@
         <v>99</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H11" s="3" t="s">
         <v>32</v>
@@ -2541,7 +2541,7 @@
         <v>78</v>
       </c>
       <c r="K11" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="12">
@@ -2555,7 +2555,7 @@
         <v>103</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E12" s="3">
         <v>83</v>
@@ -2564,7 +2564,7 @@
         <v>104</v>
       </c>
       <c r="G12" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H12" s="3" t="s">
         <v>32</v>
@@ -2576,7 +2576,7 @@
         <v>106</v>
       </c>
       <c r="K12" s="3">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
@@ -2599,7 +2599,7 @@
         <v>109</v>
       </c>
       <c r="G13" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H13" s="3" t="s">
         <v>32</v>
@@ -2611,7 +2611,7 @@
         <v>111</v>
       </c>
       <c r="K13" s="3">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="14">
@@ -2625,7 +2625,7 @@
         <v>103</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E14" s="3">
         <v>74</v>
@@ -2634,7 +2634,7 @@
         <v>113</v>
       </c>
       <c r="G14" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>32</v>
@@ -2646,7 +2646,7 @@
         <v>78</v>
       </c>
       <c r="K14" s="3">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="15">
@@ -2660,7 +2660,7 @@
         <v>117</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="3">
         <v>70</v>
@@ -2669,7 +2669,7 @@
         <v>118</v>
       </c>
       <c r="G15" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H15" s="3" t="s">
         <v>32</v>
@@ -2681,7 +2681,7 @@
         <v>67</v>
       </c>
       <c r="K15" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="16">
@@ -2695,19 +2695,19 @@
         <v>122</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E16" s="3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G16" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H16" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I16" s="3" t="s">
         <v>124</v>
@@ -2716,7 +2716,7 @@
         <v>125</v>
       </c>
       <c r="K16" s="3">
-        <v>41</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17">
@@ -2727,136 +2727,136 @@
         <v>127</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>59</v>
+        <v>128</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E17" s="3">
-        <v>61</v>
+        <v>68</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="G17" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H17" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I17" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="J17" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="K17" s="3">
-        <v>45</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="E18" s="3">
-        <v>57</v>
+        <v>68</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="G18" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H18" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I18" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>106</v>
+        <v>137</v>
       </c>
       <c r="K18" s="3">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>138</v>
+        <v>59</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E19" s="3">
-        <v>54</v>
+        <v>61</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="G19" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H19" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I19" s="3" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="J19" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="K19" s="3">
-        <v>6</v>
+        <v>46</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="D20" s="3" t="s">
         <v>28</v>
       </c>
       <c r="E20" s="3">
-        <v>46</v>
+        <v>57</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G20" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H20" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I20" s="3" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="J20" s="3" t="s">
-        <v>147</v>
+        <v>106</v>
       </c>
       <c r="K20" s="3">
-        <v>50</v>
+        <v>8</v>
       </c>
     </row>
     <row r="21">
@@ -2873,13 +2873,13 @@
         <v>26</v>
       </c>
       <c r="E21" s="3">
-        <v>39</v>
+        <v>54</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>151</v>
       </c>
       <c r="G21" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H21" s="3" t="s">
         <v>32</v>
@@ -2888,220 +2888,220 @@
         <v>152</v>
       </c>
       <c r="J21" s="3" t="s">
-        <v>67</v>
+        <v>153</v>
       </c>
       <c r="K21" s="3">
-        <v>56</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>59</v>
+        <v>134</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="E22" s="3">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G22" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H22" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I22" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="J22" s="3" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="K22" s="3">
-        <v>3</v>
+        <v>51</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="E23" s="3">
-        <v>34</v>
+        <v>41</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G23" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H23" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I23" s="3" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>163</v>
+        <v>137</v>
       </c>
       <c r="K23" s="3">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>59</v>
+        <v>166</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E24" s="3">
-        <v>28</v>
+        <v>39</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="G24" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H24" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I24" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="J24" s="3" t="s">
         <v>67</v>
       </c>
       <c r="K24" s="3">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>169</v>
+        <v>59</v>
       </c>
       <c r="D25" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E25" s="3">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="G25" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H25" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I25" s="3" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="J25" s="3" t="s">
-        <v>73</v>
+        <v>173</v>
       </c>
       <c r="K25" s="3">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="E26" s="3">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="G26" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H26" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I26" s="3" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="J26" s="3" t="s">
-        <v>90</v>
+        <v>125</v>
       </c>
       <c r="K26" s="3">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>136</v>
+        <v>169</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>184</v>
+        <v>59</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E27" s="3">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G27" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H27" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I27" s="3" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="J27" s="3" t="s">
-        <v>187</v>
+        <v>67</v>
       </c>
       <c r="K27" s="3">
-        <v>62</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28">
@@ -3112,31 +3112,31 @@
         <v>189</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>138</v>
+        <v>190</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E28" s="3">
-        <v>24</v>
+        <v>28</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G28" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H28" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I28" s="3" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>192</v>
+        <v>73</v>
       </c>
       <c r="K28" s="3">
-        <v>43</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29">
@@ -3147,206 +3147,206 @@
         <v>194</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E29" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H29" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I29" s="3" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="J29" s="3" t="s">
-        <v>157</v>
+        <v>90</v>
       </c>
       <c r="K29" s="3">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="s">
-        <v>153</v>
+        <v>148</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>144</v>
+        <v>199</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E30" s="3">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H30" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I30" s="3" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="J30" s="3" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="K30" s="3">
-        <v>57</v>
+        <v>63</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>59</v>
+        <v>150</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="E31" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G31" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H31" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I31" s="3" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="J31" s="3" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="K31" s="3">
-        <v>34</v>
+        <v>44</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>206</v>
+        <v>169</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>207</v>
+        <v>133</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D32" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="3">
+        <v>24</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E32" s="3">
-        <v>20</v>
-      </c>
-      <c r="F32" s="3" t="s">
+      <c r="G32" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H32" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I32" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="G32" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H32" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I32" s="3" t="s">
+      <c r="J32" s="3" t="s">
         <v>210</v>
       </c>
-      <c r="J32" s="3" t="s">
-        <v>211</v>
-      </c>
       <c r="K32" s="3">
-        <v>16</v>
+        <v>58</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="s">
+        <v>211</v>
+      </c>
+      <c r="B33" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="C33" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D33" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="3">
+        <v>23</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="C33" s="3" t="s">
+      <c r="G33" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H33" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I33" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E33" s="3">
-        <v>20</v>
-      </c>
-      <c r="F33" s="3" t="s">
+      <c r="J33" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="G33" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H33" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="I33" s="3" t="s">
-        <v>216</v>
-      </c>
-      <c r="J33" s="3" t="s">
-        <v>217</v>
-      </c>
       <c r="K33" s="3">
-        <v>1</v>
+        <v>35</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
+        <v>216</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>217</v>
+      </c>
+      <c r="C34" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C34" s="3" t="s">
-        <v>150</v>
-      </c>
       <c r="D34" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E34" s="3">
         <v>20</v>
       </c>
       <c r="F34" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="G34" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H34" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I34" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="G34" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="I34" s="3" t="s">
+      <c r="J34" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="J34" s="3" t="s">
-        <v>187</v>
-      </c>
       <c r="K34" s="3">
-        <v>62</v>
+        <v>17</v>
       </c>
     </row>
     <row r="35">
@@ -3357,147 +3357,147 @@
         <v>223</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>174</v>
+        <v>224</v>
       </c>
       <c r="D35" s="3" t="s">
         <v>26</v>
       </c>
       <c r="E35" s="3">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G35" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H35" s="3" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="I35" s="3" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="J35" s="3" t="s">
-        <v>73</v>
+        <v>227</v>
       </c>
       <c r="K35" s="3">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>79</v>
+        <v>228</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>144</v>
+        <v>166</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E36" s="3">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="G36" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H36" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I36" s="3" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>50</v>
+        <v>202</v>
       </c>
       <c r="K36" s="3">
-        <v>2</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>144</v>
+        <v>195</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E37" s="3">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="G37" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H37" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I37" s="3" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>233</v>
+        <v>73</v>
       </c>
       <c r="K37" s="3">
-        <v>9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>153</v>
+        <v>79</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>174</v>
+        <v>134</v>
       </c>
       <c r="D38" s="3" t="s">
         <v>25</v>
       </c>
       <c r="E38" s="3">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="G38" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H38" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I38" s="3" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="J38" s="3" t="s">
         <v>50</v>
       </c>
       <c r="K38" s="3">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>150</v>
+        <v>134</v>
       </c>
       <c r="D39" s="3" t="s">
         <v>25</v>
@@ -3506,68 +3506,68 @@
         <v>12</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="G39" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H39" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I39" s="3" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="J39" s="3" t="s">
-        <v>187</v>
+        <v>243</v>
       </c>
       <c r="K39" s="3">
-        <v>62</v>
+        <v>10</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C40" s="3" t="s">
-        <v>242</v>
+        <v>166</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E40" s="3">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="G40" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H40" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I40" s="3" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="J40" s="3" t="s">
-        <v>73</v>
+        <v>202</v>
       </c>
       <c r="K40" s="3">
-        <v>0</v>
+        <v>63</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>245</v>
+        <v>169</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>174</v>
+        <v>93</v>
       </c>
       <c r="D41" s="3" t="s">
         <v>25</v>
@@ -3576,116 +3576,118 @@
         <v>8</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="G41" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H41" s="3" t="s">
         <v>32</v>
       </c>
       <c r="I41" s="3" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="J41" s="3" t="s">
-        <v>50</v>
+        <v>137</v>
       </c>
       <c r="K41" s="3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
+        <v>251</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>252</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D42" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E42" s="3">
+        <v>8</v>
+      </c>
+      <c r="F42" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="C42" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="D42" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E42" s="3">
-        <v>4</v>
-      </c>
-      <c r="F42" s="3" t="s">
-        <v>252</v>
-      </c>
       <c r="G42" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H42" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I42" s="3" t="s">
         <v>253</v>
       </c>
       <c r="J42" s="3" t="s">
-        <v>254</v>
+        <v>50</v>
       </c>
       <c r="K42" s="3">
-        <v>14</v>
+        <v>3</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
+        <v>254</v>
+      </c>
+      <c r="B43" s="3" t="s">
         <v>255</v>
       </c>
-      <c r="B43" s="3" t="s">
+      <c r="C43" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="C43" s="3" t="s">
-        <v>257</v>
-      </c>
       <c r="D43" s="3" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E43" s="3">
         <v>4</v>
       </c>
       <c r="F43" s="3" t="s">
+        <v>257</v>
+      </c>
+      <c r="G43" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="H43" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="I43" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="G43" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="H43" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="I43" s="3" t="s">
+      <c r="J43" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="J43" s="3" t="s">
-        <v>260</v>
-      </c>
       <c r="K43" s="3">
-        <v>35</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B44" s="3" t="s">
         <v>261</v>
       </c>
-      <c r="B44" s="3" t="s">
+      <c r="C44" s="3" t="s">
         <v>262</v>
       </c>
-      <c r="C44" s="3" t="s">
+      <c r="D44" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="E44" s="3">
+        <v>4</v>
+      </c>
+      <c r="F44" s="3" t="s">
         <v>263</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="E44" s="3">
-        <v>0</v>
-      </c>
-      <c r="F44" s="3"/>
       <c r="G44" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H44" s="3" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="I44" s="3" t="s">
         <v>264</v>
@@ -3694,7 +3696,7 @@
         <v>265</v>
       </c>
       <c r="K44" s="3">
-        <v>78</v>
+        <v>36</v>
       </c>
     </row>
     <row r="45">
@@ -3708,17 +3710,17 @@
         <v>268</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E45" s="3">
         <v>0</v>
       </c>
       <c r="F45" s="3"/>
       <c r="G45" s="3" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="H45" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I45" s="3" t="s">
         <v>269</v>
@@ -3727,7 +3729,7 @@
         <v>270</v>
       </c>
       <c r="K45" s="3">
-        <v>71</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -3784,9 +3786,9 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <cols>
-    <col min="1" max="1" width="49" customWidth="1"/>
-    <col min="2" max="2" width="23" customWidth="1"/>
-    <col min="3" max="3" width="25" customWidth="1"/>
+    <col min="1" max="1" width="33" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="31" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
     <col min="5" max="5" width="60" customWidth="1"/>
     <col min="6" max="6" width="60" customWidth="1"/>
@@ -3807,10 +3809,10 @@
         <v>40</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>44</v>
@@ -3818,103 +3820,79 @@
     </row>
     <row r="2">
       <c r="A2" s="3" t="s">
-        <v>68</v>
+        <v>132</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>69</v>
+        <v>133</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>25</v>
       </c>
       <c r="D2" s="3">
-        <v>100</v>
+        <v>68</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>71</v>
+        <v>135</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>72</v>
+        <v>136</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="D3" s="3">
-        <v>28</v>
+        <v>41</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>222</v>
+        <v>169</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>223</v>
+        <v>248</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D4" s="3">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>224</v>
+        <v>249</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="G4" s="3" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="s">
-        <v>240</v>
-      </c>
-      <c r="B5" s="3" t="s">
-        <v>241</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D5" s="3">
-        <v>8</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>243</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>244</v>
-      </c>
-      <c r="G5" s="3" t="s">
-        <v>73</v>
+        <v>137</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:G5"/>
+  <autoFilter ref="A1:G4"/>
   <hyperlinks>
     <hyperlink ref="F2" r:id="rId1"/>
     <hyperlink ref="F3" r:id="rId2"/>
     <hyperlink ref="F4" r:id="rId3"/>
-    <hyperlink ref="F5" r:id="rId4"/>
   </hyperlinks>
 </worksheet>
 </file>
@@ -3943,7 +3921,7 @@
         <v>274</v>
       </c>
       <c r="B2" s="3">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>275</v>
@@ -3962,10 +3940,10 @@
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="B4" s="3">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>278</v>
@@ -3973,18 +3951,18 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>238</v>
+        <v>279</v>
       </c>
       <c r="B5" s="3">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>280</v>
+        <v>246</v>
       </c>
       <c r="B6" s="3">
         <v>22</v>
@@ -3995,18 +3973,18 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>258</v>
+        <v>282</v>
       </c>
       <c r="B7" s="3">
         <v>20</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>283</v>
+        <v>263</v>
       </c>
       <c r="B8" s="3">
         <v>20</v>
@@ -4031,7 +4009,7 @@
         <v>287</v>
       </c>
       <c r="B10" s="3">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="C10" s="3" t="s">
         <v>288</v>
@@ -4042,7 +4020,7 @@
         <v>289</v>
       </c>
       <c r="B11" s="3">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C11" s="3" t="s">
         <v>290</v>
@@ -4053,7 +4031,7 @@
         <v>291</v>
       </c>
       <c r="B12" s="3">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="C12" s="3" t="s">
         <v>292</v>
@@ -4064,7 +4042,7 @@
         <v>293</v>
       </c>
       <c r="B13" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C13" s="3" t="s">
         <v>294</v>
@@ -4075,7 +4053,7 @@
         <v>295</v>
       </c>
       <c r="B14" s="3">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>296</v>
@@ -4153,7 +4131,7 @@
         <v>27</v>
       </c>
       <c r="B4" s="3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>305</v>
@@ -4164,7 +4142,7 @@
         <v>28</v>
       </c>
       <c r="B5" s="3">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C5" s="3" t="s">
         <v>306</v>
@@ -4224,7 +4202,7 @@
         <v>33</v>
       </c>
       <c r="B2" s="3">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="3" t="s">
         <v>312</v>
@@ -4236,7 +4214,7 @@
         <v>32</v>
       </c>
       <c r="B3" s="3">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C3" s="3" t="s">
         <v>312</v>
@@ -4248,7 +4226,7 @@
         <v>34</v>
       </c>
       <c r="B4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" s="3" t="s">
         <v>312</v>
